--- a/Student Performance.xlsx
+++ b/Student Performance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594D595B-7337-467E-A44F-A6CEADD6231A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE564794-2E8C-4B07-A72E-61D0FA6AB962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="18900" windowHeight="11055" xr2:uid="{A3D35911-DB36-4D1F-9B2A-21F25508FA1D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="1" xr2:uid="{A3D35911-DB36-4D1F-9B2A-21F25508FA1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="35">
   <si>
     <t>Name</t>
   </si>
@@ -98,6 +98,39 @@
   </si>
   <si>
     <t>Absent</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>18/06/2026</t>
+  </si>
+  <si>
+    <t>19/06/2026</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>21/06/2026</t>
+  </si>
+  <si>
+    <t>20/06/2026</t>
   </si>
 </sst>
 </file>
@@ -694,221 +727,559 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E71D60B9-395F-40CF-B351-E21BEE723D8A}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
       <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
         <v>21</v>
       </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
         <v>21</v>
       </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
       <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
       <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
         <v>22</v>
       </c>
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
       <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
       <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>10</v>
       </c>
       <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="C19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
       <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
       <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
-        <v>20</v>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Student Performance.xlsx
+++ b/Student Performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE564794-2E8C-4B07-A72E-61D0FA6AB962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0954613-0D21-4578-90D9-66D541FA60A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="1" xr2:uid="{A3D35911-DB36-4D1F-9B2A-21F25508FA1D}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="37">
   <si>
     <t>Name</t>
   </si>
@@ -127,10 +127,16 @@
     <t>Saturday</t>
   </si>
   <si>
-    <t>21/06/2026</t>
-  </si>
-  <si>
     <t>20/06/2026</t>
+  </si>
+  <si>
+    <t>22/06/2026</t>
+  </si>
+  <si>
+    <t>24/06/2026</t>
+  </si>
+  <si>
+    <t>23/6/2026</t>
   </si>
 </sst>
 </file>
@@ -197,12 +203,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -727,7 +734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E71D60B9-395F-40CF-B351-E21BEE723D8A}">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
@@ -1178,7 +1185,7 @@
         <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s">
         <v>20</v>
@@ -1192,7 +1199,7 @@
         <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D38" t="s">
         <v>20</v>
@@ -1206,7 +1213,7 @@
         <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D40" t="s">
         <v>20</v>
@@ -1220,7 +1227,7 @@
         <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D41" t="s">
         <v>20</v>
@@ -1234,7 +1241,7 @@
         <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D42" t="s">
         <v>20</v>
@@ -1248,7 +1255,7 @@
         <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>23</v>
@@ -1262,7 +1269,7 @@
         <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>23</v>
@@ -1276,10 +1283,178 @@
         <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D48" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D52" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" t="s">
+        <v>35</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
